--- a/importaciones_productos/FEE87198 registro productos.xlsx
+++ b/importaciones_productos/FEE87198 registro productos.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AMIBCAINSg</t>
+          <t>AMIBCAg</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>VITNICUSPg</t>
+          <t>NIAg</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>SOYEMUg</t>
+          <t>CITMAGFCCg</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>SOYPRO 900 EMULSION</t>
+          <t>CITRATO DE MAGNESIO FCC/MAGNESIUM CITRATE</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>18.09</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="6">
@@ -635,12 +635,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CITMAGFCCg</t>
+          <t>SOYEMUg</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>CITRATO DE MAGNESIO FCC/MAGNESIUM CITRATE</t>
+          <t>SOYPRO 900 EMULSION</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>11.3</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="7">
@@ -668,7 +668,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>COLPOLHIDg</t>
+          <t>COLHIDg</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
